--- a/jira_export_2026-10-23.xlsx
+++ b/jira_export_2026-10-23.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>398 h</t>
+          <t>402 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -2173,7 +2173,7 @@
         <v>1</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>282.5</v>
       </c>
       <c r="P20" s="15" t="n">
-        <v>376.67</v>
+        <v>282.5</v>
       </c>
     </row>
     <row r="21">
@@ -5717,7 +5717,7 @@
         <v>4</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>1242.9</v>
       </c>
       <c r="P70" s="15" t="n">
-        <v>75.33</v>
+        <v>71.02</v>
       </c>
     </row>
     <row r="71">
@@ -6933,7 +6933,7 @@
         <v>5</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>112.5</v>
       </c>
       <c r="P87" s="12" t="n">
-        <v>31.03</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88">
@@ -7005,7 +7005,7 @@
         <v>5</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="C126" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D126" s="14" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="C128" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D128" s="14" t="inlineStr">
@@ -12287,7 +12287,7 @@
         <v>4</v>
       </c>
       <c r="K166" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L166" s="14" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -12735,7 +12735,7 @@
         <v>16</v>
       </c>
       <c r="K174" s="14" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L174" s="14" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -12774,7 +12774,7 @@
         <v>49557.76700000001</v>
       </c>
       <c r="P175" s="18" t="n">
-        <v>189.28</v>
+        <v>187.84</v>
       </c>
     </row>
   </sheetData>
@@ -14247,26 +14247,26 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>173.75</v>
+        <v>175.25</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>23.75</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>9.33</v>
+        <v>9.83</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>206.83</v>
+        <v>208.83</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>32.5</v>
+        <v>34.5</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>508.2</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>41.1%</t>
         </is>
       </c>
     </row>

--- a/jira_export_2026-10-23.xlsx
+++ b/jira_export_2026-10-23.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>402 h</t>
+          <t>413 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P175"/>
+  <dimension ref="A1:P176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE D'AIX-MARSEILLE-PROVENCE] - New - LiExp</t>
+          <t>[METROPOLE D'AIX-MARSEILLE-PROVENCE] - Déploiement de Littéralis Expert (+SIREO)</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE D'AIX-MARSEILLE-PROVENCE] - New - LiExp</t>
+          <t>[METROPOLE D'AIX-MARSEILLE-PROVENCE] - Déploiement de Littéralis Expert (+SIREO)</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE D'AIX-MARSEILLE-PROVENCE] - New - LiExp</t>
+          <t>[METROPOLE D'AIX-MARSEILLE-PROVENCE] - Déploiement de Littéralis Expert (+SIREO)</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE D'AIX-MARSEILLE-PROVENCE] - New - LiExp</t>
+          <t>[METROPOLE D'AIX-MARSEILLE-PROVENCE] - Déploiement de Littéralis Expert (+SIREO)</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -5077,7 +5077,7 @@
         <v>4</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>19</v>
+        <v>21.5</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>1152</v>
       </c>
       <c r="P61" s="12" t="n">
-        <v>60.63</v>
+        <v>53.58</v>
       </c>
     </row>
     <row r="62">
@@ -5717,7 +5717,7 @@
         <v>4</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>1242.9</v>
       </c>
       <c r="P70" s="15" t="n">
-        <v>71.02</v>
+        <v>67.18000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
@@ -10792,22 +10792,22 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E142" s="14" t="n">
@@ -10825,28 +10825,28 @@
       </c>
       <c r="H142" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
         <v>19</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M142" s="14" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N142" s="15" t="n">
@@ -10862,12 +10862,12 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
@@ -10877,13 +10877,11 @@
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E143" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="n">
+        <v/>
       </c>
       <c r="F143" s="11" t="inlineStr">
         <is>
@@ -10892,27 +10890,35 @@
       </c>
       <c r="G143" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L143" s="11" t="inlineStr"/>
-      <c r="M143" s="11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L143" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M143" s="11" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N143" s="12" t="n">
         <v>0</v>
       </c>
@@ -10926,26 +10932,28 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
-        </is>
-      </c>
-      <c r="E144" s="14" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E144" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F144" s="14" t="inlineStr">
         <is>
@@ -10964,14 +10972,14 @@
       </c>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J144" s="14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K144" s="14" t="n">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="L144" s="14" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -10988,22 +10996,22 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
@@ -11021,7 +11029,7 @@
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I145" s="11" t="inlineStr">
@@ -11033,7 +11041,7 @@
         <v>22</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L145" s="11" t="inlineStr"/>
       <c r="M145" s="11" t="inlineStr"/>
@@ -11050,22 +11058,22 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C146" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E146" s="14" t="n">
@@ -11073,44 +11081,36 @@
       </c>
       <c r="F146" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G146" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H146" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J146" s="14" t="n">
         <v>22</v>
       </c>
       <c r="K146" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L146" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M146" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L146" s="14" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
       <c r="N146" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O146" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P146" s="15" t="n">
@@ -11120,22 +11120,22 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="F147" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr">
@@ -11153,34 +11153,34 @@
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J147" s="11" t="n">
         <v>22</v>
       </c>
       <c r="K147" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M147" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N147" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O147" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O147" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P147" s="12" t="n">
@@ -11190,22 +11190,22 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B148" s="14" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C148" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E148" s="14" t="n">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="G148" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H148" s="14" t="inlineStr">
@@ -11228,17 +11228,25 @@
       </c>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J148" s="14" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K148" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="L148" s="14" t="inlineStr"/>
-      <c r="M148" s="14" t="inlineStr"/>
+      <c r="L148" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M148" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N148" s="15" t="n">
         <v>0</v>
       </c>
@@ -11252,12 +11260,12 @@
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15041</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
@@ -11267,7 +11275,7 @@
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>CD38</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
@@ -11290,14 +11298,14 @@
       </c>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J149" s="11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L149" s="11" t="inlineStr"/>
       <c r="M149" s="11" t="inlineStr"/>
@@ -11314,22 +11322,22 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C150" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E150" s="14" t="n">
@@ -11352,14 +11360,14 @@
       </c>
       <c r="I150" s="14" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J150" s="14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K150" s="14" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L150" s="14" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -11376,12 +11384,12 @@
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr">
@@ -11391,7 +11399,7 @@
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E151" s="11" t="n">
@@ -11414,14 +11422,14 @@
       </c>
       <c r="I151" s="11" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J151" s="11" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K151" s="11" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="L151" s="11" t="inlineStr"/>
       <c r="M151" s="11" t="inlineStr"/>
@@ -11438,12 +11446,12 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B152" s="14" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C152" s="14" t="inlineStr">
@@ -11453,7 +11461,7 @@
       </c>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E152" s="14" t="n">
@@ -11471,19 +11479,19 @@
       </c>
       <c r="H152" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I152" s="14" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J152" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K152" s="14" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="L152" s="14" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -11500,12 +11508,12 @@
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr">
@@ -11515,7 +11523,7 @@
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E153" s="11" t="n">
@@ -11528,35 +11536,27 @@
       </c>
       <c r="G153" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I153" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J153" s="11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K153" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L153" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M153" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L153" s="11" t="inlineStr"/>
+      <c r="M153" s="11" t="inlineStr"/>
       <c r="N153" s="12" t="n">
         <v>0</v>
       </c>
@@ -11570,22 +11570,22 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B154" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C154" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D154" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E154" s="14" t="n">
@@ -11598,23 +11598,35 @@
       </c>
       <c r="G154" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H154" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H154" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I154" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J154" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K154" s="14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L154" s="14" t="inlineStr"/>
-      <c r="M154" s="14" t="inlineStr"/>
+        <v>1.25</v>
+      </c>
+      <c r="L154" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M154" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N154" s="15" t="n">
         <v>0</v>
       </c>
@@ -11628,12 +11640,12 @@
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr">
@@ -11643,7 +11655,7 @@
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E155" s="11" t="n">
@@ -11659,32 +11671,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H155" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H155" s="11" t="inlineStr"/>
       <c r="I155" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J155" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K155" s="11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L155" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M155" s="11" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>3.75</v>
+      </c>
+      <c r="L155" s="11" t="inlineStr"/>
+      <c r="M155" s="11" t="inlineStr"/>
       <c r="N155" s="12" t="n">
         <v>0</v>
       </c>
@@ -11698,22 +11698,22 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B156" s="14" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C156" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D156" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E156" s="14" t="n">
@@ -11726,29 +11726,33 @@
       </c>
       <c r="G156" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H156" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H156" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I156" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J156" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K156" s="14" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="L156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
+          <t>PDMDEP-34532</t>
         </is>
       </c>
       <c r="M156" s="14" t="inlineStr">
         <is>
-          <t>424152</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="N156" s="15" t="n">
@@ -11764,24 +11768,26 @@
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C157" s="11" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C157" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E157" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E157" s="11" t="n">
+        <v/>
       </c>
       <c r="F157" s="11" t="inlineStr">
         <is>
@@ -11790,27 +11796,31 @@
       </c>
       <c r="G157" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H157" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H157" s="11" t="inlineStr"/>
       <c r="I157" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J157" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K157" s="11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L157" s="11" t="inlineStr"/>
-      <c r="M157" s="11" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L157" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M157" s="11" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
       <c r="N157" s="12" t="n">
         <v>0</v>
       </c>
@@ -11824,21 +11834,25 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>PSC-1363</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B158" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C158" s="14" t="inlineStr"/>
       <c r="D158" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
-        </is>
-      </c>
-      <c r="E158" s="14" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E158" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F158" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11846,20 +11860,24 @@
       </c>
       <c r="G158" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H158" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H158" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I158" s="14" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J158" s="14" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K158" s="14" t="n">
-        <v>0.25</v>
+        <v>2.25</v>
       </c>
       <c r="L158" s="14" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -11876,46 +11894,50 @@
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>PSC-1357</t>
+          <t>PSC-1363</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS - FDS</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr"/>
-      <c r="D159" s="11" t="inlineStr"/>
+      <c r="D159" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE DE CADENET</t>
+        </is>
+      </c>
       <c r="E159" s="11" t="inlineStr"/>
-      <c r="F159" s="11" t="inlineStr"/>
+      <c r="F159" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G159" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr"/>
       <c r="I159" s="11" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="J159" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K159" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L159" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-36143</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L159" s="11" t="inlineStr"/>
       <c r="M159" s="11" t="inlineStr"/>
       <c r="N159" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O159" s="12" t="n">
-        <v>210.8</v>
+        <v>0</v>
       </c>
       <c r="P159" s="12" t="n">
         <v>0</v>
@@ -11924,50 +11946,46 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>PSC-1351</t>
+          <t>PSC-1357</t>
         </is>
       </c>
       <c r="B160" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE BALLAINVILLIERS - FDS</t>
         </is>
       </c>
       <c r="C160" s="14" t="inlineStr"/>
-      <c r="D160" s="14" t="inlineStr">
-        <is>
-          <t>COMMUNE DE VALENCAY</t>
-        </is>
-      </c>
+      <c r="D160" s="14" t="inlineStr"/>
       <c r="E160" s="14" t="inlineStr"/>
-      <c r="F160" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+      <c r="F160" s="14" t="inlineStr"/>
       <c r="G160" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H160" s="14" t="inlineStr"/>
       <c r="I160" s="14" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="J160" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K160" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L160" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L160" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-36143</t>
+        </is>
+      </c>
       <c r="M160" s="14" t="inlineStr"/>
       <c r="N160" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O160" s="15" t="n">
-        <v>0</v>
+        <v>210.8</v>
       </c>
       <c r="P160" s="15" t="n">
         <v>0</v>
@@ -11976,18 +11994,18 @@
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>PSC-1346</t>
+          <t>PSC-1351</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr"/>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr"/>
@@ -12004,7 +12022,7 @@
       <c r="H161" s="11" t="inlineStr"/>
       <c r="I161" s="11" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J161" s="11" t="n">
@@ -12028,18 +12046,18 @@
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1346</t>
         </is>
       </c>
       <c r="B162" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="C162" s="14" t="inlineStr"/>
       <c r="D162" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="E162" s="14" t="inlineStr"/>
@@ -12050,56 +12068,48 @@
       </c>
       <c r="G162" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H162" s="14" t="inlineStr"/>
       <c r="I162" s="14" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J162" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K162" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L162" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M162" s="14" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+      <c r="L162" s="14" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
       <c r="N162" s="15" t="n">
-        <v>450</v>
-      </c>
-      <c r="O162" s="16" t="n">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="O162" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="P162" s="15" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="10" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C163" s="11" t="inlineStr"/>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr"/>
@@ -12110,13 +12120,13 @@
       </c>
       <c r="G163" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr"/>
       <c r="I163" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J163" s="11" t="n">
@@ -12125,33 +12135,41 @@
       <c r="K163" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L163" s="11" t="inlineStr"/>
-      <c r="M163" s="11" t="inlineStr"/>
+      <c r="L163" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M163" s="11" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N163" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O163" s="12" t="n">
-        <v>0</v>
+        <v>450</v>
+      </c>
+      <c r="O163" s="16" t="n">
+        <v>50</v>
       </c>
       <c r="P163" s="12" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B164" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C164" s="14" t="inlineStr"/>
       <c r="D164" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E164" s="14" t="inlineStr"/>
@@ -12162,13 +12180,13 @@
       </c>
       <c r="G164" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H164" s="14" t="inlineStr"/>
       <c r="I164" s="14" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J164" s="14" t="n">
@@ -12177,16 +12195,8 @@
       <c r="K164" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L164" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M164" s="14" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+      <c r="L164" s="14" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
       <c r="N164" s="15" t="n">
         <v>0</v>
       </c>
@@ -12200,18 +12210,18 @@
     <row r="165">
       <c r="A165" s="10" t="inlineStr">
         <is>
-          <t>PSC-1305</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C165" s="11" t="inlineStr"/>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr"/>
@@ -12222,23 +12232,31 @@
       </c>
       <c r="G165" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr"/>
       <c r="I165" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J165" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K165" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L165" s="11" t="inlineStr"/>
-      <c r="M165" s="11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L165" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34778</t>
+        </is>
+      </c>
+      <c r="M165" s="11" t="inlineStr">
+        <is>
+          <t>00172868</t>
+        </is>
+      </c>
       <c r="N165" s="12" t="n">
         <v>0</v>
       </c>
@@ -12252,18 +12270,18 @@
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>PSC-1300</t>
+          <t>PSC-1305</t>
         </is>
       </c>
       <c r="B166" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="C166" s="14" t="inlineStr"/>
       <c r="D166" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="E166" s="14" t="inlineStr"/>
@@ -12280,7 +12298,7 @@
       <c r="H166" s="14" t="inlineStr"/>
       <c r="I166" s="14" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J166" s="14" t="n">
@@ -12304,18 +12322,18 @@
     <row r="167">
       <c r="A167" s="10" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C167" s="11" t="inlineStr"/>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr"/>
@@ -12332,14 +12350,14 @@
       <c r="H167" s="11" t="inlineStr"/>
       <c r="I167" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J167" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K167" s="11" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="L167" s="11" t="inlineStr"/>
       <c r="M167" s="11" t="inlineStr"/>
@@ -12356,18 +12374,18 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B168" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C168" s="14" t="inlineStr"/>
       <c r="D168" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E168" s="14" t="inlineStr"/>
@@ -12378,31 +12396,23 @@
       </c>
       <c r="G168" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H168" s="14" t="inlineStr"/>
       <c r="I168" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J168" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K168" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L168" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34335</t>
-        </is>
-      </c>
-      <c r="M168" s="14" t="inlineStr">
-        <is>
-          <t>00168072</t>
-        </is>
-      </c>
+        <v>0.33</v>
+      </c>
+      <c r="L168" s="14" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
       <c r="N168" s="15" t="n">
         <v>0</v>
       </c>
@@ -12416,18 +12426,18 @@
     <row r="169">
       <c r="A169" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C169" s="11" t="inlineStr"/>
       <c r="D169" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr"/>
@@ -12444,23 +12454,23 @@
       <c r="H169" s="11" t="inlineStr"/>
       <c r="I169" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J169" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K169" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L169" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-34335</t>
         </is>
       </c>
       <c r="M169" s="11" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00168072</t>
         </is>
       </c>
       <c r="N169" s="12" t="n">
@@ -12476,18 +12486,18 @@
     <row r="170">
       <c r="A170" s="13" t="inlineStr">
         <is>
-          <t>PSC-1264</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B170" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C170" s="14" t="inlineStr"/>
       <c r="D170" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E170" s="14" t="inlineStr"/>
@@ -12498,23 +12508,31 @@
       </c>
       <c r="G170" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H170" s="14" t="inlineStr"/>
       <c r="I170" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J170" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K170" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L170" s="14" t="inlineStr"/>
-      <c r="M170" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L170" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M170" s="14" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N170" s="15" t="n">
         <v>0</v>
       </c>
@@ -12528,18 +12546,18 @@
     <row r="171">
       <c r="A171" s="10" t="inlineStr">
         <is>
-          <t>PSC-1119</t>
+          <t>PSC-1264</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>BETSCHDORF</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="C171" s="11" t="inlineStr"/>
       <c r="D171" s="11" t="inlineStr">
         <is>
-          <t>BETSCHDORF</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr"/>
@@ -12550,31 +12568,23 @@
       </c>
       <c r="G171" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H171" s="11" t="inlineStr"/>
       <c r="I171" s="11" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J171" s="11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K171" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L171" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-30236</t>
-        </is>
-      </c>
-      <c r="M171" s="11" t="inlineStr">
-        <is>
-          <t>00152992</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L171" s="11" t="inlineStr"/>
+      <c r="M171" s="11" t="inlineStr"/>
       <c r="N171" s="12" t="n">
         <v>0</v>
       </c>
@@ -12588,18 +12598,18 @@
     <row r="172">
       <c r="A172" s="13" t="inlineStr">
         <is>
-          <t>PSC-1060</t>
+          <t>PSC-1119</t>
         </is>
       </c>
       <c r="B172" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE COUBLEVIE</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="C172" s="14" t="inlineStr"/>
       <c r="D172" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE COUBLEVIE</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="E172" s="14" t="inlineStr"/>
@@ -12610,23 +12620,31 @@
       </c>
       <c r="G172" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H172" s="14" t="inlineStr"/>
       <c r="I172" s="14" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="J172" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K172" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L172" s="14" t="inlineStr"/>
-      <c r="M172" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L172" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-30236</t>
+        </is>
+      </c>
+      <c r="M172" s="14" t="inlineStr">
+        <is>
+          <t>00152992</t>
+        </is>
+      </c>
       <c r="N172" s="15" t="n">
         <v>0</v>
       </c>
@@ -12640,18 +12658,18 @@
     <row r="173">
       <c r="A173" s="10" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PSC-1060</t>
         </is>
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="C173" s="11" t="inlineStr"/>
       <c r="D173" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr"/>
@@ -12662,31 +12680,23 @@
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H173" s="11" t="inlineStr"/>
       <c r="I173" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="J173" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K173" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L173" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-26768</t>
-        </is>
-      </c>
-      <c r="M173" s="11" t="inlineStr">
-        <is>
-          <t>00141775</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L173" s="11" t="inlineStr"/>
+      <c r="M173" s="11" t="inlineStr"/>
       <c r="N173" s="12" t="n">
         <v>0</v>
       </c>
@@ -12700,18 +12710,18 @@
     <row r="174">
       <c r="A174" s="13" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-1047</t>
         </is>
       </c>
       <c r="B174" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="C174" s="14" t="inlineStr"/>
       <c r="D174" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="E174" s="14" t="inlineStr"/>
@@ -12722,59 +12732,119 @@
       </c>
       <c r="G174" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H174" s="14" t="inlineStr"/>
       <c r="I174" s="14" t="inlineStr">
         <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="J174" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="K174" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L174" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-26768</t>
+        </is>
+      </c>
+      <c r="M174" s="14" t="inlineStr">
+        <is>
+          <t>00141775</t>
+        </is>
+      </c>
+      <c r="N174" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="10" t="inlineStr">
+        <is>
+          <t>PSC-850</t>
+        </is>
+      </c>
+      <c r="B175" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="C175" s="11" t="inlineStr"/>
+      <c r="D175" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="E175" s="11" t="inlineStr"/>
+      <c r="F175" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G175" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H175" s="11" t="inlineStr"/>
+      <c r="I175" s="11" t="inlineStr">
+        <is>
           <t>10/06/2025</t>
         </is>
       </c>
-      <c r="J174" s="14" t="n">
+      <c r="J175" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="K174" s="14" t="n">
+      <c r="K175" s="11" t="n">
         <v>0.75</v>
       </c>
-      <c r="L174" s="14" t="inlineStr"/>
-      <c r="M174" s="14" t="inlineStr"/>
-      <c r="N174" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O174" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P174" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="17" t="inlineStr">
+      <c r="L175" s="11" t="inlineStr"/>
+      <c r="M175" s="11" t="inlineStr"/>
+      <c r="N175" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B175" s="17" t="inlineStr"/>
-      <c r="C175" s="17" t="inlineStr"/>
-      <c r="D175" s="17" t="inlineStr"/>
-      <c r="E175" s="17" t="inlineStr"/>
-      <c r="F175" s="17" t="inlineStr"/>
-      <c r="G175" s="17" t="inlineStr"/>
-      <c r="H175" s="17" t="inlineStr"/>
-      <c r="I175" s="17" t="inlineStr"/>
-      <c r="J175" s="17" t="inlineStr"/>
-      <c r="K175" s="17" t="inlineStr"/>
-      <c r="L175" s="17" t="inlineStr"/>
-      <c r="M175" s="17" t="inlineStr"/>
-      <c r="N175" s="18" t="n">
+      <c r="B176" s="17" t="inlineStr"/>
+      <c r="C176" s="17" t="inlineStr"/>
+      <c r="D176" s="17" t="inlineStr"/>
+      <c r="E176" s="17" t="inlineStr"/>
+      <c r="F176" s="17" t="inlineStr"/>
+      <c r="G176" s="17" t="inlineStr"/>
+      <c r="H176" s="17" t="inlineStr"/>
+      <c r="I176" s="17" t="inlineStr"/>
+      <c r="J176" s="17" t="inlineStr"/>
+      <c r="K176" s="17" t="inlineStr"/>
+      <c r="L176" s="17" t="inlineStr"/>
+      <c r="M176" s="17" t="inlineStr"/>
+      <c r="N176" s="18" t="n">
         <v>90876.166</v>
       </c>
-      <c r="O175" s="18" t="n">
+      <c r="O176" s="18" t="n">
         <v>49557.76700000001</v>
       </c>
-      <c r="P175" s="18" t="n">
-        <v>187.84</v>
+      <c r="P176" s="18" t="n">
+        <v>184.69</v>
       </c>
     </row>
   </sheetData>
@@ -12950,6 +13020,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId169"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId171"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14247,7 +14318,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>175.25</v>
+        <v>179.75</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>23.75</v>
@@ -14256,17 +14327,17 @@
         <v>9.83</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>208.83</v>
+        <v>213.33</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>34.5</v>
+        <v>38</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>508.2</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>42.0%</t>
         </is>
       </c>
     </row>
@@ -14308,7 +14379,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>99.33</v>
+        <v>102.33</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-10-23.xlsx
+++ b/jira_export_2026-10-23.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>413 h</t>
+          <t>427 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -5717,7 +5717,7 @@
         <v>4</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>1242.9</v>
       </c>
       <c r="P70" s="15" t="n">
-        <v>67.18000000000001</v>
+        <v>62.15</v>
       </c>
     </row>
     <row r="71">
@@ -6933,7 +6933,7 @@
         <v>5</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>3.75</v>
+        <v>4.88</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>112.5</v>
       </c>
       <c r="P87" s="12" t="n">
-        <v>30</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="88">
@@ -7005,7 +7005,7 @@
         <v>5</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>3.75</v>
+        <v>4.88</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>9</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>9.25</v>
+        <v>10.25</v>
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>22</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="L145" s="11" t="inlineStr"/>
       <c r="M145" s="11" t="inlineStr"/>
@@ -12844,7 +12844,7 @@
         <v>49557.76700000001</v>
       </c>
       <c r="P176" s="18" t="n">
-        <v>184.69</v>
+        <v>181.3</v>
       </c>
     </row>
   </sheetData>
@@ -13032,7 +13032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -13058,7 +13058,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tickets 'Matériel GEODP' clôturés ce mois — 13 ligne(s)</t>
+          <t>Tickets 'Matériel GEODP' clôturés ce mois — 15 ligne(s)</t>
         </is>
       </c>
     </row>
@@ -13176,22 +13176,22 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35597</t>
+          <t>PDMDEP-36205</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Acquisition et paramétrage 2 PAXA920 Pro </t>
+          <t xml:space="preserve">[COMME DE FECAMP] - Migration GEODP + mise en service paiement cb et 1 TPE </t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMME DE FECAMP</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acquisition et paramétrage 2 PAXA920 Pro </t>
+          <t xml:space="preserve">Migration GEODP + mise en service paiement cb et 1 TPE </t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -13214,37 +13214,37 @@
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35604</t>
+          <t>PDMDEP-36212</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>00181048</t>
+          <t>00176660</t>
         </is>
       </c>
       <c r="K6" s="15" t="n">
-        <v>1630</v>
+        <v>815</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35469</t>
+          <t>PDMDEP-35597</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VENCE] -  Migration GeODP Placier Terrasse</t>
+          <t xml:space="preserve">[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Acquisition et paramétrage 2 PAXA920 Pro </t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VENCE</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
+          <t xml:space="preserve">Acquisition et paramétrage 2 PAXA920 Pro </t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -13267,37 +13267,37 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35476</t>
+          <t>PDMDEP-35604</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>00180644</t>
+          <t>00181048</t>
         </is>
       </c>
       <c r="K7" s="12" t="n">
-        <v>815</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35227</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE CHAUNY] - Migration de GEODP-Placier + Remise en service paiement cb + Pax + Formation </t>
+          <t>[COMMUNE DE VENCE] -  Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHAUNY</t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration de GEODP-Placier + Remise en service paiement cb + Pax + Formation </t>
+          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35234</t>
+          <t>PDMDEP-35476</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>00179117</t>
+          <t>00180644</t>
         </is>
       </c>
       <c r="K8" s="15" t="n">
@@ -13335,22 +13335,22 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34287</t>
+          <t>PDMDEP-35227</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
+          <t xml:space="preserve">[VILLE DE CHAUNY] - Migration de GEODP-Placier + Remise en service paiement cb + Pax + Formation </t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>VILLE DE CHAUNY</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP </t>
+          <t xml:space="preserve">Migration de GEODP-Placier + Remise en service paiement cb + Pax + Formation </t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -13373,37 +13373,37 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34294</t>
+          <t>PDMDEP-35234</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>00171435</t>
+          <t>00179117</t>
         </is>
       </c>
       <c r="K9" s="12" t="n">
-        <v>1630</v>
+        <v>815</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -13426,37 +13426,37 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34256</t>
+          <t>PDMDEP-34294</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>00171362</t>
+          <t>00171435</t>
         </is>
       </c>
       <c r="K10" s="15" t="n">
-        <v>815</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="H11" s="11" t="n">
@@ -13479,12 +13479,12 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34199</t>
+          <t>PDMDEP-34256</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>00171163</t>
+          <t>00171362</t>
         </is>
       </c>
       <c r="K11" s="12" t="n">
@@ -13494,22 +13494,22 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Migration module Placier</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="H12" s="14" t="n">
@@ -13532,37 +13532,37 @@
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34019</t>
+          <t>PDMDEP-34199</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>00170492</t>
+          <t>00171163</t>
         </is>
       </c>
       <c r="K12" s="15" t="n">
-        <v>1630</v>
+        <v>815</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Migration module Placier</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -13585,37 +13585,37 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33848</t>
+          <t>PDMDEP-34019</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>00161104</t>
+          <t>00170492</t>
         </is>
       </c>
       <c r="K13" s="12" t="n">
-        <v>815</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33686</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>[EUROMETROPOLE DE METZ] - Paiement CB + 3 PAX</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>EUROMETROPOLE DE METZ</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Paiement CB + 3 PAX</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="H14" s="14" t="n">
@@ -13638,37 +13638,37 @@
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33692</t>
+          <t>PDMDEP-33848</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>00169320</t>
+          <t>00161104</t>
         </is>
       </c>
       <c r="K14" s="15" t="n">
-        <v>2445</v>
+        <v>815</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33149</t>
+          <t>PDMDEP-33686</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
+          <t>[EUROMETROPOLE DE METZ] - Paiement CB + 3 PAX</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
+          <t>EUROMETROPOLE DE METZ</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP</t>
+          <t>Paiement CB + 3 PAX</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="H15" s="11" t="n">
@@ -13691,37 +13691,37 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33156</t>
+          <t>PDMDEP-33692</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>00165721</t>
+          <t>00169320</t>
         </is>
       </c>
       <c r="K15" s="12" t="n">
-        <v>815</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-33149</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration GeODP</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -13744,12 +13744,12 @@
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31819</t>
+          <t>PDMDEP-33156</t>
         </is>
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>00159472</t>
+          <t>00165721</t>
         </is>
       </c>
       <c r="K16" s="15" t="n">
@@ -13759,73 +13759,179 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
+          <t>PDMDEP-32193</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MONTAUBAN</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Migration GEODP2</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-32200</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>00160783</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-31812</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE PROVINS</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Migration V2 classique</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31819</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>00159472</t>
+        </is>
+      </c>
+      <c r="K18" s="15" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
           <t>PDMDEP-31479</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Migration vers GeoDP V2</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="H17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="H19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-31486</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>00157474</t>
         </is>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>815</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr"/>
-      <c r="C18" s="17" t="inlineStr"/>
-      <c r="D18" s="17" t="inlineStr"/>
-      <c r="E18" s="17" t="inlineStr"/>
-      <c r="F18" s="17" t="inlineStr"/>
-      <c r="G18" s="17" t="inlineStr"/>
-      <c r="H18" s="17" t="inlineStr"/>
-      <c r="I18" s="17" t="inlineStr"/>
-      <c r="J18" s="17" t="inlineStr"/>
-      <c r="K18" s="18" t="n">
-        <v>14670</v>
+      <c r="B20" s="17" t="inlineStr"/>
+      <c r="C20" s="17" t="inlineStr"/>
+      <c r="D20" s="17" t="inlineStr"/>
+      <c r="E20" s="17" t="inlineStr"/>
+      <c r="F20" s="17" t="inlineStr"/>
+      <c r="G20" s="17" t="inlineStr"/>
+      <c r="H20" s="17" t="inlineStr"/>
+      <c r="I20" s="17" t="inlineStr"/>
+      <c r="J20" s="17" t="inlineStr"/>
+      <c r="K20" s="18" t="n">
+        <v>17115</v>
       </c>
     </row>
   </sheetData>
@@ -13844,6 +13950,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14318,16 +14426,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>179.75</v>
+        <v>184.5</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>23.75</v>
+        <v>24</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>9.83</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>213.33</v>
+        <v>218.33</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>38</v>
@@ -14337,7 +14445,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>43.0%</t>
         </is>
       </c>
     </row>
@@ -14379,7 +14487,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>102.33</v>
+        <v>111.83</v>
       </c>
     </row>
   </sheetData>
@@ -14464,10 +14572,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>476341</v>
+        <v>477591</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>201513</v>
+        <v>202763</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>274829</v>
@@ -14489,10 +14597,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>254623</v>
+        <v>255873</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>67511</v>
+        <v>68761</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>187112</v>
@@ -14543,7 +14651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -14567,7 +14675,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 18 commande(s)</t>
+          <t>Épics créées ce mois — 19 commande(s)</t>
         </is>
       </c>
     </row>
@@ -14622,22 +14730,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36519</t>
+          <t>PDMDEP-36581</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36510</t>
+          <t>PDMDEP-36572</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LANCON PROVENCE</t>
+          <t>MAIRIE EYMET</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -14647,7 +14755,7 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -14657,7 +14765,7 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00185247</t>
+          <t>00185751</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
@@ -14667,22 +14775,22 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36474</t>
+          <t>PDMDEP-36519</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36465</t>
+          <t>PDMDEP-36510</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SALON DE PROVENCE</t>
+          <t>COMMUNE DE LANCON PROVENCE</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -14702,32 +14810,32 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00185032</t>
+          <t>00185247</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>4685</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36459</t>
+          <t>PDMDEP-36214</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36453</t>
+          <t>PDMDEP-36205</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE EVREUX </t>
+          <t>COMME DE FECAMP</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -14737,7 +14845,7 @@
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -14747,32 +14855,32 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>00184982</t>
+          <t>00176659</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
-        <v>895</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36214</t>
+          <t>PDMDEP-36474</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36205</t>
+          <t>PDMDEP-36465</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>COMME DE FECAMP</t>
+          <t>COMMUNE DE SALON DE PROVENCE</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -14792,32 +14900,32 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00176659</t>
+          <t>00185032</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>2500</v>
+        <v>4685</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36236</t>
+          <t>PDMDEP-36459</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36230</t>
+          <t>PDMDEP-36453</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIBERON</t>
+          <t xml:space="preserve">COMMUNE DE EVREUX </t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -14837,32 +14945,32 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00183980</t>
+          <t>00184982</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>985</v>
+        <v>895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36335</t>
+          <t>PDMDEP-36236</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36327</t>
+          <t>PDMDEP-36230</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>VILLE D'AIGLE</t>
+          <t>COMMUNE DE QUIBERON</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -14882,32 +14990,32 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00184406</t>
+          <t>00183980</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>500</v>
+        <v>985</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36181</t>
+          <t>PDMDEP-36335</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36174</t>
+          <t>PDMDEP-36327</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE AURAY</t>
+          <t>VILLE D'AIGLE</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -14917,7 +15025,7 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -14927,32 +15035,32 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>00183814</t>
+          <t>00184406</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
-        <v>1800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36387</t>
+          <t>PDMDEP-36349</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36381</t>
+          <t>PDMDEP-36345</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRIANCON</t>
+          <t>MAIRIE DE LEUCATE Service Achat</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -14962,7 +15070,7 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -14972,7 +15080,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00184667</t>
+          <t>00184482</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
@@ -14982,22 +15090,22 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36376</t>
+          <t>PDMDEP-36181</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36370</t>
+          <t>PDMDEP-36174</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SALON DE PROVENCE</t>
+          <t>COMMUNE DE AURAY</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -15007,7 +15115,7 @@
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -15017,32 +15125,32 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>00184665</t>
+          <t>00183814</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36349</t>
+          <t>PDMDEP-36387</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36345</t>
+          <t>PDMDEP-36381</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LEUCATE Service Achat</t>
+          <t>COMMUNE DE BRIANCON</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -15052,7 +15160,7 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -15062,7 +15170,7 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>00184482</t>
+          <t>00184667</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
@@ -15072,27 +15180,27 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36555</t>
+          <t>PDMDEP-36376</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36549</t>
+          <t>PDMDEP-36370</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE SALON DE PROVENCE</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
@@ -15107,7 +15215,7 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>00185556</t>
+          <t>00184665</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
@@ -15336,28 +15444,28 @@
         </is>
       </c>
       <c r="I20" s="26" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36427</t>
+          <t>PDMDEP-36555</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36421</t>
+          <t>PDMDEP-36549</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
@@ -15377,83 +15485,107 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>00184846</t>
+          <t>00185556</t>
         </is>
       </c>
       <c r="I21" s="25" t="n">
-        <v>3575</v>
+        <v>750</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-36427</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36421</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>00184846</t>
+        </is>
+      </c>
+      <c r="I22" s="26" t="n">
+        <v>3575</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-36148</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-36144</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>VILLE DE VILLEFRANCHE SUR SAONE</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>00183228</t>
         </is>
       </c>
-      <c r="I22" s="26" t="n">
+      <c r="I23" s="25" t="n">
         <v>2310</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="17" t="n"/>
-      <c r="F23" s="17" t="n"/>
-      <c r="G23" s="17" t="n"/>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>18 commande(s)</t>
-        </is>
-      </c>
-      <c r="I23" s="24" t="n">
-        <v>26968</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B24" s="17" t="n"/>
@@ -15464,17 +15596,17 @@
       <c r="G24" s="17" t="n"/>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>8 commande(s)</t>
+          <t>19 commande(s)</t>
         </is>
       </c>
       <c r="I24" s="24" t="n">
-        <v>15603</v>
+        <v>28218</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B25" s="17" t="n"/>
@@ -15485,10 +15617,31 @@
       <c r="G25" s="17" t="n"/>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>10 commande(s)</t>
+          <t>8 commande(s)</t>
         </is>
       </c>
       <c r="I25" s="24" t="n">
+        <v>16853</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
+      <c r="G26" s="17" t="n"/>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
+          <t>11 commande(s)</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="n">
         <v>11365</v>
       </c>
     </row>
